--- a/data/trans_orig/P16A15-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A15-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>18630</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38742</t>
+          <t>39761</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56491</t>
+          <t>55002</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435034</t>
+          <t>434015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455672</t>
+          <t>455146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283196</t>
+          <t>283622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299545</t>
+          <t>298535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>723966</t>
+          <t>725455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>751544</t>
+          <t>750983</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30323</t>
+          <t>28604</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43413</t>
+          <t>43574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336611</t>
+          <t>338330</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354127</t>
+          <t>355096</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352306</t>
+          <t>351948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366063</t>
+          <t>366254</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>695386</t>
+          <t>695225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718028</t>
+          <t>717099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42055</t>
+          <t>43149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30856</t>
+          <t>30125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55148</t>
+          <t>55199</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500334</t>
+          <t>499240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521262</t>
+          <t>521248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148832</t>
+          <t>149420</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161872</t>
+          <t>162116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>655023</t>
+          <t>654972</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>679315</t>
+          <t>680046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75768</t>
+          <t>75736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111518</t>
+          <t>111400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30750</t>
+          <t>31108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53760</t>
+          <t>54867</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114069</t>
+          <t>114694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155101</t>
+          <t>158105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1126816</t>
+          <t>1126934</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1162566</t>
+          <t>1162598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>660525</t>
+          <t>659418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>683535</t>
+          <t>683177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1797519</t>
+          <t>1794515</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1838551</t>
+          <t>1837926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>25097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33640</t>
+          <t>32334</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59730</t>
+          <t>58308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>47740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76424</t>
+          <t>77453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324922</t>
+          <t>324440</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339430</t>
+          <t>338896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>509022</t>
+          <t>510444</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535112</t>
+          <t>536418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>841865</t>
+          <t>840836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871903</t>
+          <t>870549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122614</t>
+          <t>121621</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166422</t>
+          <t>169799</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124318</t>
+          <t>124457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171656</t>
+          <t>170631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289705</t>
+          <t>290223</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297323</t>
+          <t>297324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1082338</t>
+          <t>1078961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1126146</t>
+          <t>1127139</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1375304</t>
+          <t>1376329</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1422642</t>
+          <t>1422503</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162631</t>
+          <t>164647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>217863</t>
+          <t>218093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>233841</t>
+          <t>237666</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>300449</t>
+          <t>299767</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>417975</t>
+          <t>415522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>498433</t>
+          <t>496595</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3051309</t>
+          <t>3051079</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3106541</t>
+          <t>3104525</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3077675</t>
+          <t>3078357</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3144283</t>
+          <t>3140458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6148863</t>
+          <t>6150701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6229321</t>
+          <t>6231774</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27723</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54291</t>
+          <t>54942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28060</t>
+          <t>28418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42528</t>
+          <t>42435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74077</t>
+          <t>74162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>382107</t>
+          <t>381456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408675</t>
+          <t>408512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286394</t>
+          <t>286036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304115</t>
+          <t>303999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676775</t>
+          <t>676690</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>708324</t>
+          <t>708417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52512</t>
+          <t>51649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14083</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>33368</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45580</t>
+          <t>45471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77053</t>
+          <t>77984</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364506</t>
+          <t>365369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389335</t>
+          <t>389453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>301145</t>
+          <t>301947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321232</t>
+          <t>322212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675280</t>
+          <t>674349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>706753</t>
+          <t>706862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59146</t>
+          <t>59163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92842</t>
+          <t>93629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33174</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78059</t>
+          <t>76118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117533</t>
+          <t>115333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535487</t>
+          <t>534700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>569183</t>
+          <t>569166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224764</t>
+          <t>227076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244192</t>
+          <t>245144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>768734</t>
+          <t>770934</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>808208</t>
+          <t>810149</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117754</t>
+          <t>118280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163218</t>
+          <t>164438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>48172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79429</t>
+          <t>80617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175288</t>
+          <t>174843</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231508</t>
+          <t>232605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>994912</t>
+          <t>993692</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1040376</t>
+          <t>1039850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>687228</t>
+          <t>686040</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>719827</t>
+          <t>718485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1693280</t>
+          <t>1692183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1749500</t>
+          <t>1749945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45524</t>
+          <t>46022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74352</t>
+          <t>74801</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94273</t>
+          <t>96802</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137192</t>
+          <t>137230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150991</t>
+          <t>151084</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>203422</t>
+          <t>200676</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>436244</t>
+          <t>435795</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465072</t>
+          <t>464574</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>621032</t>
+          <t>620994</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>663951</t>
+          <t>661422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1065399</t>
+          <t>1068145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1117830</t>
+          <t>1117737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>171044</t>
+          <t>173070</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>223794</t>
+          <t>227257</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>175808</t>
+          <t>176530</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>229953</t>
+          <t>230550</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255099</t>
+          <t>254256</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>882506</t>
+          <t>879043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>935256</t>
+          <t>933230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1142188</t>
+          <t>1141591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1196333</t>
+          <t>1195611</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>313100</t>
+          <t>316306</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>391299</t>
+          <t>389987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>395630</t>
+          <t>396206</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>475938</t>
+          <t>481647</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>730485</t>
+          <t>733799</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>839948</t>
+          <t>840851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3025014</t>
+          <t>3026326</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3103213</t>
+          <t>3100007</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3062951</t>
+          <t>3057242</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3143259</t>
+          <t>3142683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6115253</t>
+          <t>6114350</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6224716</t>
+          <t>6221402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>25685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50247</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36465</t>
+          <t>38350</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67392</t>
+          <t>66711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378845</t>
+          <t>379473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402898</t>
+          <t>403407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>321239</t>
+          <t>321636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338868</t>
+          <t>339565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>708755</t>
+          <t>709436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>739682</t>
+          <t>737797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43344</t>
+          <t>42664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35511</t>
+          <t>35488</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,47 +6396,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>9,53%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>54384</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>41323</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>71477</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>9,54%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>54384</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>40742</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>70787</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>333883</t>
+          <t>334563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355977</t>
+          <t>355080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336762</t>
+          <t>336785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357873</t>
+          <t>356758</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,47 +6509,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>90,47%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>95,83%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>695116</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>678023</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>708177</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>90,46%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>695116</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>678713</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>708758</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>90,56%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46064</t>
+          <t>46567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74847</t>
+          <t>76195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32284</t>
+          <t>31048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64462</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99692</t>
+          <t>99658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>447067</t>
+          <t>445719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>475850</t>
+          <t>475347</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133839</t>
+          <t>135075</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153428</t>
+          <t>153686</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>588344</t>
+          <t>588378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623574</t>
+          <t>623825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98605</t>
+          <t>98898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141574</t>
+          <t>140040</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41847</t>
+          <t>41639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70451</t>
+          <t>69973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151235</t>
+          <t>149219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199342</t>
+          <t>202479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1008064</t>
+          <t>1009598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1051033</t>
+          <t>1050740</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>755425</t>
+          <t>755903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>784029</t>
+          <t>784237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1776172</t>
+          <t>1773035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1824279</t>
+          <t>1826295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55157</t>
+          <t>57150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85581</t>
+          <t>86640</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79865</t>
+          <t>83196</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120127</t>
+          <t>119557</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147309</t>
+          <t>146861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196614</t>
+          <t>196730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>535125</t>
+          <t>534066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>565549</t>
+          <t>563556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>618117</t>
+          <t>618687</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>658379</t>
+          <t>655048</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1162336</t>
+          <t>1162220</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1211641</t>
+          <t>1212089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>147783</t>
+          <t>148118</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>200224</t>
+          <t>201074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>152164</t>
+          <t>150502</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205183</t>
+          <t>204067</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>278866</t>
+          <t>279555</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>881801</t>
+          <t>880951</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>934242</t>
+          <t>933907</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1163987</t>
+          <t>1165103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1217006</t>
+          <t>1218668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>288285</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>354139</t>
+          <t>351079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>351381</t>
+          <t>348619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>426558</t>
+          <t>428172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>656883</t>
+          <t>650291</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>762422</t>
+          <t>759840</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3031583</t>
+          <t>3034643</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3097437</t>
+          <t>3102499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3105038</t>
+          <t>3103424</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3180215</t>
+          <t>3182977</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6154896</t>
+          <t>6157478</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6260435</t>
+          <t>6267027</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47314</t>
+          <t>48129</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74228</t>
+          <t>74592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38277</t>
+          <t>37391</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58992</t>
+          <t>58846</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92102</t>
+          <t>91672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124057</t>
+          <t>124357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430984</t>
+          <t>430620</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>457898</t>
+          <t>457083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388475</t>
+          <t>388621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>409190</t>
+          <t>410076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>828622</t>
+          <t>828322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>860577</t>
+          <t>861007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50063</t>
+          <t>50620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77367</t>
+          <t>78100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27530</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44710</t>
+          <t>45520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82335</t>
+          <t>84510</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114578</t>
+          <t>115999</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374846</t>
+          <t>374113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402150</t>
+          <t>401593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337870</t>
+          <t>337060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355050</t>
+          <t>355201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720215</t>
+          <t>718794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752458</t>
+          <t>750283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21877</t>
+          <t>24287</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106085</t>
+          <t>109976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21304</t>
+          <t>21110</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34462</t>
+          <t>35510</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37136</t>
+          <t>36646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135419</t>
+          <t>133905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>562179</t>
+          <t>558288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646387</t>
+          <t>643977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132449</t>
+          <t>131401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145607</t>
+          <t>145801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>699756</t>
+          <t>701270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>798039</t>
+          <t>798529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>125198</t>
+          <t>125731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>166189</t>
+          <t>166392</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100128</t>
+          <t>101283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>611136</t>
+          <t>619281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>245574</t>
+          <t>245688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>940145</t>
+          <t>973535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>868630</t>
+          <t>868427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>909621</t>
+          <t>909088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366392</t>
+          <t>358247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>877400</t>
+          <t>876245</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1072202</t>
+          <t>1038812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1766773</t>
+          <t>1766659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45154</t>
+          <t>45524</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71777</t>
+          <t>71851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107905</t>
+          <t>108222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169537</t>
+          <t>168734</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167660</t>
+          <t>164598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225949</t>
+          <t>227118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>402272</t>
+          <t>402198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428895</t>
+          <t>428525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>669459</t>
+          <t>670262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>731091</t>
+          <t>730774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1087096</t>
+          <t>1085927</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1145385</t>
+          <t>1148447</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>113732</t>
+          <t>115386</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147533</t>
+          <t>145659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116793</t>
+          <t>116868</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149773</t>
+          <t>150388</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232308</t>
+          <t>232206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239038</t>
+          <t>239061</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>612619</t>
+          <t>614493</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>646420</t>
+          <t>644766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>850886</t>
+          <t>850271</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883866</t>
+          <t>883791</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>306014</t>
+          <t>298733</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>439828</t>
+          <t>437922</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>484184</t>
+          <t>484840</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1210637</t>
+          <t>1226402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>860897</t>
+          <t>852789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1590199</t>
+          <t>1704581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2935236</t>
+          <t>2937142</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3069050</t>
+          <t>3076331</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2362997</t>
+          <t>2347232</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3089450</t>
+          <t>3088794</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5358498</t>
+          <t>5244116</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6087800</t>
+          <t>6095908</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A15-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A15-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39761</t>
+          <t>41187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>22644</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>29185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55002</t>
+          <t>55757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>434015</t>
+          <t>432589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455146</t>
+          <t>454923</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283622</t>
+          <t>284036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298535</t>
+          <t>299447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>725455</t>
+          <t>724700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750983</t>
+          <t>751272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>29744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19917</t>
+          <t>20012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21700</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43574</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338330</t>
+          <t>337190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355096</t>
+          <t>354135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351948</t>
+          <t>351853</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366254</t>
+          <t>366571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>695225</t>
+          <t>695901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>717099</t>
+          <t>717573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43149</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30125</t>
+          <t>30229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55199</t>
+          <t>55676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499240</t>
+          <t>498190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521248</t>
+          <t>521348</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149420</t>
+          <t>148432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162116</t>
+          <t>161839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654972</t>
+          <t>654495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680046</t>
+          <t>679942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75736</t>
+          <t>74902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111400</t>
+          <t>110846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31108</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54867</t>
+          <t>53690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114694</t>
+          <t>113833</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158105</t>
+          <t>159068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1126934</t>
+          <t>1127488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1162598</t>
+          <t>1163432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>659418</t>
+          <t>660595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>683177</t>
+          <t>684276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1794515</t>
+          <t>1793552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1837926</t>
+          <t>1838787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25097</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32334</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58308</t>
+          <t>58622</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47740</t>
+          <t>47443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77453</t>
+          <t>78469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324440</t>
+          <t>324104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338896</t>
+          <t>339611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>510444</t>
+          <t>510130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>536418</t>
+          <t>535230</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>840836</t>
+          <t>839820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>870549</t>
+          <t>870846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>121621</t>
+          <t>124284</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>169799</t>
+          <t>166908</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124457</t>
+          <t>123529</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170631</t>
+          <t>170745</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290223</t>
+          <t>290297</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297324</t>
+          <t>297328</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1078961</t>
+          <t>1081852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1127139</t>
+          <t>1124476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1376329</t>
+          <t>1376215</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1422503</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>164647</t>
+          <t>164427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>218093</t>
+          <t>214944</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>237666</t>
+          <t>238703</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>299767</t>
+          <t>301162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>415522</t>
+          <t>413384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>496595</t>
+          <t>496162</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3051079</t>
+          <t>3054228</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3104525</t>
+          <t>3104745</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3078357</t>
+          <t>3076962</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3140458</t>
+          <t>3139421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6150701</t>
+          <t>6151134</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6231774</t>
+          <t>6233912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54942</t>
+          <t>54888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28418</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74162</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381456</t>
+          <t>381510</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408512</t>
+          <t>408368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286036</t>
+          <t>286645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303999</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676690</t>
+          <t>675428</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>708417</t>
+          <t>707911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27565</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51649</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33368</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>45815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77984</t>
+          <t>77239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365369</t>
+          <t>365913</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389453</t>
+          <t>390669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>301947</t>
+          <t>301804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322212</t>
+          <t>321818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674349</t>
+          <t>675094</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>706862</t>
+          <t>706518</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59163</t>
+          <t>57760</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93629</t>
+          <t>92547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30862</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76118</t>
+          <t>75854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115333</t>
+          <t>116990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534700</t>
+          <t>535782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>569166</t>
+          <t>570569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227076</t>
+          <t>226850</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245144</t>
+          <t>245097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>770934</t>
+          <t>769277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>810149</t>
+          <t>810413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118280</t>
+          <t>116968</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>164438</t>
+          <t>164682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48172</t>
+          <t>46036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80617</t>
+          <t>80227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174843</t>
+          <t>171672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232605</t>
+          <t>229246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>993692</t>
+          <t>993448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1039850</t>
+          <t>1041162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>686040</t>
+          <t>686430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>718485</t>
+          <t>720621</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1692183</t>
+          <t>1695542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1749945</t>
+          <t>1753116</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46022</t>
+          <t>45042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74801</t>
+          <t>74174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96802</t>
+          <t>97351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137230</t>
+          <t>138295</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151084</t>
+          <t>150410</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200676</t>
+          <t>201421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>435795</t>
+          <t>436422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>464574</t>
+          <t>465554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>620994</t>
+          <t>619929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>661422</t>
+          <t>660873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1068145</t>
+          <t>1067400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1117737</t>
+          <t>1118411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>173070</t>
+          <t>171788</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>227257</t>
+          <t>225266</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>176530</t>
+          <t>174292</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>230550</t>
+          <t>225719</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254256</t>
+          <t>255098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>879043</t>
+          <t>881034</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>933230</t>
+          <t>934512</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1141591</t>
+          <t>1146422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1195611</t>
+          <t>1197849</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>316306</t>
+          <t>313448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>389987</t>
+          <t>387081</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>396206</t>
+          <t>394921</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>481647</t>
+          <t>479310</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>733799</t>
+          <t>735100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>840851</t>
+          <t>840748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3026326</t>
+          <t>3029232</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3100007</t>
+          <t>3102865</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3057242</t>
+          <t>3059579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3142683</t>
+          <t>3143968</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6114350</t>
+          <t>6114453</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6221402</t>
+          <t>6220101</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25685</t>
+          <t>25949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49619</t>
+          <t>51067</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25419</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38350</t>
+          <t>37260</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66711</t>
+          <t>66644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379473</t>
+          <t>378025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403407</t>
+          <t>403143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>321636</t>
+          <t>322078</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339565</t>
+          <t>339279</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>709436</t>
+          <t>709503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>737797</t>
+          <t>738887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>21228</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42664</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35488</t>
+          <t>36210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41323</t>
+          <t>40471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71477</t>
+          <t>69594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>334563</t>
+          <t>333805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355080</t>
+          <t>355999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336785</t>
+          <t>336063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>356758</t>
+          <t>357172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678023</t>
+          <t>679906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>708177</t>
+          <t>709029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46567</t>
+          <t>47057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76195</t>
+          <t>75371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64211</t>
+          <t>64435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99658</t>
+          <t>98713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>445719</t>
+          <t>446543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>475347</t>
+          <t>474857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135075</t>
+          <t>133754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153686</t>
+          <t>153147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>588378</t>
+          <t>589323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623825</t>
+          <t>623601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98898</t>
+          <t>100488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140040</t>
+          <t>138890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41639</t>
+          <t>42402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69973</t>
+          <t>72780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149219</t>
+          <t>148179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202479</t>
+          <t>198813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1009598</t>
+          <t>1010748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1050740</t>
+          <t>1049150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>755903</t>
+          <t>753096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>784237</t>
+          <t>783474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1773035</t>
+          <t>1776701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1826295</t>
+          <t>1827335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57150</t>
+          <t>56070</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86640</t>
+          <t>86888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83196</t>
+          <t>82832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119557</t>
+          <t>122530</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146861</t>
+          <t>144970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196730</t>
+          <t>196083</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>534066</t>
+          <t>533818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>563556</t>
+          <t>564636</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>618687</t>
+          <t>615714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>655048</t>
+          <t>655412</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1162220</t>
+          <t>1162867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1212089</t>
+          <t>1213980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>148118</t>
+          <t>150894</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>201074</t>
+          <t>200776</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>150502</t>
+          <t>150476</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>204067</t>
+          <t>204969</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279555</t>
+          <t>278630</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>880951</t>
+          <t>881249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>933907</t>
+          <t>931131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1165103</t>
+          <t>1164201</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1218668</t>
+          <t>1218694</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>287889</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>351079</t>
+          <t>352557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>348619</t>
+          <t>350503</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>650291</t>
+          <t>657489</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>759840</t>
+          <t>761846</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3034643</t>
+          <t>3033165</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3102499</t>
+          <t>3097833</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3182977</t>
+          <t>3181093</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6157478</t>
+          <t>6155472</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6267027</t>
+          <t>6259829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>59764</t>
+          <t>65036</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48129</t>
+          <t>53311</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74592</t>
+          <t>79525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>51134</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37391</t>
+          <t>40537</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58846</t>
+          <t>64417</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>106739</t>
+          <t>116170</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91672</t>
+          <t>99833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124357</t>
+          <t>134598</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>445448</t>
+          <t>485582</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430620</t>
+          <t>471093</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>457083</t>
+          <t>497307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>400491</t>
+          <t>437277</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388621</t>
+          <t>423994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>410076</t>
+          <t>447874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>845940</t>
+          <t>922859</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>828322</t>
+          <t>904431</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>861007</t>
+          <t>939196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62667</t>
+          <t>67018</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50620</t>
+          <t>53809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78100</t>
+          <t>82162</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35541</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27379</t>
+          <t>29796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45520</t>
+          <t>48791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>98208</t>
+          <t>105727</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84510</t>
+          <t>88994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115999</t>
+          <t>124035</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>389546</t>
+          <t>416194</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374113</t>
+          <t>401050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401593</t>
+          <t>429403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>347039</t>
+          <t>384434</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337060</t>
+          <t>374352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355201</t>
+          <t>393347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>736585</t>
+          <t>800628</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>718794</t>
+          <t>782320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>750283</t>
+          <t>817361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>68113</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24287</t>
+          <t>55490</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109976</t>
+          <t>83923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>23443</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35510</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>91415</t>
+          <t>98295</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36646</t>
+          <t>83226</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133905</t>
+          <t>114704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>604469</t>
+          <t>403499</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558288</t>
+          <t>387689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643977</t>
+          <t>416122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>139291</t>
+          <t>157315</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131401</t>
+          <t>148146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145801</t>
+          <t>164054</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>743760</t>
+          <t>560814</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>701270</t>
+          <t>544405</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>798529</t>
+          <t>575883</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>144714</t>
+          <t>153998</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>125731</t>
+          <t>133959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>166392</t>
+          <t>175106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>287807</t>
+          <t>91792</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101283</t>
+          <t>79602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>619281</t>
+          <t>108643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>432521</t>
+          <t>245791</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>245688</t>
+          <t>220048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>973535</t>
+          <t>271844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>890105</t>
+          <t>977845</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>868427</t>
+          <t>956737</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>909088</t>
+          <t>997884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>689721</t>
+          <t>768823</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>358247</t>
+          <t>751972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>876245</t>
+          <t>781013</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1579826</t>
+          <t>1746667</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1038812</t>
+          <t>1720614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1766659</t>
+          <t>1772410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>57448</t>
+          <t>60926</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45524</t>
+          <t>50665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71851</t>
+          <t>76190</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,67 +10040,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>145586</t>
+          <t>159047</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108222</t>
+          <t>142865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168734</t>
+          <t>177978</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>19,16%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>219973</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>199988</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>242342</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>15,74%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>14,31%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>17,35%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>20,11%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>203034</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>164598</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>227118</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>12,54%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>416601</t>
+          <t>506050</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>402198</t>
+          <t>490786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428525</t>
+          <t>516311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,67 +10153,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>693410</t>
+          <t>671080</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>670262</t>
+          <t>652149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>730774</t>
+          <t>687262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>80,84%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>78,56%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>82,79%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1177130</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1154761</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1197115</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>84,26%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>82,65%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>79,89%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1450</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1110011</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1085927</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1148447</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>84,54%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>82,7%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>129274</t>
+          <t>141332</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115386</t>
+          <t>125376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145659</t>
+          <t>158000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>132928</t>
+          <t>144975</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116868</t>
+          <t>127717</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150388</t>
+          <t>164093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236853</t>
+          <t>233585</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232206</t>
+          <t>228916</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239061</t>
+          <t>235898</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>630878</t>
+          <t>701661</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>614493</t>
+          <t>684993</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>644766</t>
+          <t>717617</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>867731</t>
+          <t>935246</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>850271</t>
+          <t>916128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883791</t>
+          <t>952504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,18%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>392041</t>
+          <t>418734</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>298733</t>
+          <t>383820</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>437922</t>
+          <t>453558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>672804</t>
+          <t>512196</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>484840</t>
+          <t>482665</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1226402</t>
+          <t>546884</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1064845</t>
+          <t>930931</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>852789</t>
+          <t>883201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1704581</t>
+          <t>980171</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2983023</t>
+          <t>3022754</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2937142</t>
+          <t>2987930</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3076331</t>
+          <t>3057668</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2900830</t>
+          <t>3120590</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2347232</t>
+          <t>3085902</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3088794</t>
+          <t>3150121</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5883852</t>
+          <t>6143344</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5244116</t>
+          <t>6094104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6095908</t>
+          <t>6191074</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6948697</t>
+          <t>7074275</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6948697</t>
+          <t>7074275</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6948697</t>
+          <t>7074275</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
